--- a/Excel/StoreConfig.xlsx
+++ b/Excel/StoreConfig.xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="254" uniqueCount="149">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="261" uniqueCount="151">
   <si>
     <t>#</t>
   </si>
@@ -70,6 +70,9 @@
     <t>Fee</t>
   </si>
   <si>
+    <t>Cycle</t>
+  </si>
+  <si>
     <t>Des</t>
   </si>
   <si>
@@ -479,6 +482,9 @@
   </si>
   <si>
     <t>爆率+50%</t>
+  </si>
+  <si>
+    <t>节日祝福图</t>
   </si>
 </sst>
 </file>
@@ -1450,37 +1456,37 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C1:P66"/>
+  <dimension ref="C1:Q68"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" customHeight="1"/>
   <cols>
     <col min="1" max="3" width="9" style="1"/>
     <col min="4" max="4" width="12.625" style="1" customWidth="1"/>
     <col min="5" max="5" width="15.9166666666667" style="1" customWidth="1"/>
     <col min="6" max="10" width="12.25" style="1" customWidth="1"/>
-    <col min="11" max="13" width="11.125" style="1" customWidth="1"/>
-    <col min="14" max="14" width="24.875" style="1" customWidth="1"/>
-    <col min="15" max="15" width="39.25" style="1" customWidth="1"/>
-    <col min="16" max="16" width="43" style="1" customWidth="1"/>
-    <col min="17" max="16384" width="9" style="1"/>
+    <col min="11" max="14" width="11.125" style="1" customWidth="1"/>
+    <col min="15" max="15" width="24.875" style="1" customWidth="1"/>
+    <col min="16" max="16" width="39.25" style="1" customWidth="1"/>
+    <col min="17" max="17" width="43" style="1" customWidth="1"/>
+    <col min="18" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" customHeight="1" spans="3:16">
-      <c r="O1" s="1" t="s">
-        <v>0</v>
-      </c>
+    <row r="1" customHeight="1" spans="3:17">
       <c r="P1" s="1" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="2" customHeight="1" spans="3:16">
-      <c r="O2" s="1" t="s">
-        <v>0</v>
-      </c>
+      <c r="Q1" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" customHeight="1" spans="3:17">
       <c r="P2" s="1" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="3" s="1" customFormat="1" customHeight="1" spans="3:16">
+      <c r="Q2" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" s="1" customFormat="1" customHeight="1" spans="3:17">
       <c r="C3" s="3" t="s">
         <v>1</v>
       </c>
@@ -1517,8 +1523,11 @@
       <c r="N3" s="3" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="4" s="1" customFormat="1" customHeight="1" spans="3:16">
+      <c r="O3" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="4" s="1" customFormat="1" customHeight="1" spans="3:17">
       <c r="C4" s="3" t="s">
         <v>1</v>
       </c>
@@ -1555,57 +1564,63 @@
       <c r="N4" s="3" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="5" s="1" customFormat="1" customHeight="1" spans="3:16">
+      <c r="O4" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="5" s="1" customFormat="1" customHeight="1" spans="3:17">
       <c r="C5" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D5" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="G5" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="E5" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="F5" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="G5" s="3" t="s">
-        <v>13</v>
-      </c>
       <c r="H5" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K5" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="L5" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="M5" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="N5" s="3" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="6" customHeight="1" spans="3:16">
+      <c r="O5" s="3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="6" customHeight="1" spans="3:17">
       <c r="C6" s="1">
         <v>1001</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E6" s="7" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F6" s="7" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="H6" s="1">
         <v>0</v>
@@ -1625,22 +1640,25 @@
       <c r="M6" s="1">
         <v>88</v>
       </c>
-      <c r="O6" s="2" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="7" customHeight="1" spans="3:16">
+      <c r="N6" s="1">
+        <v>1</v>
+      </c>
+      <c r="P6" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="7" customHeight="1" spans="3:17">
       <c r="C7" s="1">
         <v>1002</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E7" s="7" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F7" s="7" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H7" s="1">
         <v>0</v>
@@ -1660,22 +1678,25 @@
       <c r="M7" s="1">
         <v>88</v>
       </c>
-      <c r="O7" s="2" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="8" customHeight="1" spans="3:16">
+      <c r="N7" s="1">
+        <v>1</v>
+      </c>
+      <c r="P7" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="8" customHeight="1" spans="3:17">
       <c r="C8" s="1">
         <v>1003</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E8" s="7" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F8" s="7" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H8" s="1">
         <v>0</v>
@@ -1695,22 +1716,25 @@
       <c r="M8" s="1">
         <v>88</v>
       </c>
-      <c r="O8" s="1" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="9" customHeight="1" spans="3:16">
+      <c r="N8" s="1">
+        <v>1</v>
+      </c>
+      <c r="P8" s="1" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="9" customHeight="1" spans="3:17">
       <c r="C9" s="1">
         <v>1004</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E9" s="7" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F9" s="7" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="H9" s="1">
         <v>0</v>
@@ -1730,22 +1754,25 @@
       <c r="M9" s="1">
         <v>88</v>
       </c>
-      <c r="O9" s="1" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="10" s="2" customFormat="1" customHeight="1" spans="3:16">
+      <c r="N9" s="1">
+        <v>1</v>
+      </c>
+      <c r="P9" s="1" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="10" s="2" customFormat="1" customHeight="1" spans="3:17">
       <c r="C10" s="1">
         <v>1005</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E10" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F10" s="7" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G10" s="1"/>
       <c r="H10" s="1">
@@ -1766,22 +1793,25 @@
       <c r="M10" s="1">
         <v>88</v>
       </c>
-      <c r="O10" s="1" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="11" s="2" customFormat="1" customHeight="1" spans="3:16">
+      <c r="N10" s="1">
+        <v>1</v>
+      </c>
+      <c r="P10" s="1" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="11" s="2" customFormat="1" customHeight="1" spans="3:17">
       <c r="C11" s="1">
         <v>1006</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E11" s="7" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F11" s="7" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G11" s="1"/>
       <c r="H11" s="1">
@@ -1802,11 +1832,14 @@
       <c r="M11" s="1">
         <v>88</v>
       </c>
-      <c r="O11" s="1" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="12" s="2" customFormat="1" customHeight="1" spans="3:16">
+      <c r="N11" s="1">
+        <v>1</v>
+      </c>
+      <c r="P11" s="1" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="12" s="2" customFormat="1" customHeight="1" spans="3:17">
       <c r="C12" s="1"/>
       <c r="D12" s="1"/>
       <c r="E12" s="1"/>
@@ -1818,20 +1851,21 @@
       <c r="K12" s="1"/>
       <c r="L12" s="1"/>
       <c r="M12" s="1"/>
-      <c r="O12" s="1"/>
-    </row>
-    <row r="13" s="2" customFormat="1" customHeight="1" spans="3:16">
+      <c r="N12" s="1"/>
+      <c r="P12" s="1"/>
+    </row>
+    <row r="13" s="2" customFormat="1" customHeight="1" spans="3:17">
       <c r="C13" s="1">
         <v>2001</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E13" s="7" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F13" s="7" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G13" s="1"/>
       <c r="H13" s="1">
@@ -1852,22 +1886,25 @@
       <c r="M13" s="1">
         <v>288</v>
       </c>
-      <c r="O13" s="2" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="14" s="2" customFormat="1" customHeight="1" spans="3:16">
+      <c r="N13" s="1">
+        <v>1</v>
+      </c>
+      <c r="P13" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="14" s="2" customFormat="1" customHeight="1" spans="3:17">
       <c r="C14" s="1">
         <v>2002</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E14" s="7" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F14" s="7" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="G14" s="1"/>
       <c r="H14" s="1">
@@ -1888,22 +1925,25 @@
       <c r="M14" s="1">
         <v>288</v>
       </c>
-      <c r="O14" s="2" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="15" s="2" customFormat="1" customHeight="1" spans="3:16">
+      <c r="N14" s="1">
+        <v>1</v>
+      </c>
+      <c r="P14" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="15" s="2" customFormat="1" customHeight="1" spans="3:17">
       <c r="C15" s="1">
         <v>2003</v>
       </c>
       <c r="D15" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="E15" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="F15" s="7" t="s">
         <v>41</v>
-      </c>
-      <c r="E15" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="F15" s="7" t="s">
-        <v>40</v>
       </c>
       <c r="G15" s="1"/>
       <c r="H15" s="1">
@@ -1924,22 +1964,25 @@
       <c r="M15" s="1">
         <v>288</v>
       </c>
-      <c r="O15" s="1" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="16" s="2" customFormat="1" customHeight="1" spans="3:16">
+      <c r="N15" s="1">
+        <v>1</v>
+      </c>
+      <c r="P15" s="1" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="16" s="2" customFormat="1" customHeight="1" spans="3:17">
       <c r="C16" s="1">
         <v>2004</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E16" s="7" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F16" s="7" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="G16" s="1"/>
       <c r="H16" s="1">
@@ -1960,22 +2003,25 @@
       <c r="M16" s="1">
         <v>288</v>
       </c>
-      <c r="O16" s="1" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="17" s="2" customFormat="1" customHeight="1" spans="3:15">
+      <c r="N16" s="1">
+        <v>1</v>
+      </c>
+      <c r="P16" s="1" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="17" s="2" customFormat="1" customHeight="1" spans="3:16">
       <c r="C17" s="1">
         <v>2005</v>
       </c>
       <c r="D17" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="E17" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="F17" s="7" t="s">
         <v>44</v>
-      </c>
-      <c r="E17" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="F17" s="7" t="s">
-        <v>43</v>
       </c>
       <c r="G17" s="1"/>
       <c r="H17" s="1">
@@ -1996,22 +2042,25 @@
       <c r="M17" s="1">
         <v>288</v>
       </c>
-      <c r="O17" s="1" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="18" s="2" customFormat="1" customHeight="1" spans="3:15">
+      <c r="N17" s="1">
+        <v>1</v>
+      </c>
+      <c r="P17" s="1" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="18" s="2" customFormat="1" customHeight="1" spans="3:16">
       <c r="C18" s="1">
         <v>2006</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E18" s="7" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F18" s="7" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="G18" s="1"/>
       <c r="H18" s="1">
@@ -2032,22 +2081,25 @@
       <c r="M18" s="1">
         <v>288</v>
       </c>
-      <c r="O18" s="1" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="19" s="2" customFormat="1" customHeight="1" spans="3:15">
+      <c r="N18" s="1">
+        <v>1</v>
+      </c>
+      <c r="P18" s="1" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="19" s="2" customFormat="1" customHeight="1" spans="3:16">
       <c r="C19" s="1">
         <v>2007</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E19" s="7" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F19" s="7" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="G19" s="1"/>
       <c r="H19" s="1">
@@ -2068,22 +2120,25 @@
       <c r="M19" s="1">
         <v>288</v>
       </c>
-      <c r="O19" s="2" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="20" s="2" customFormat="1" customHeight="1" spans="3:15">
+      <c r="N19" s="1">
+        <v>1</v>
+      </c>
+      <c r="P19" s="2" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="20" s="2" customFormat="1" customHeight="1" spans="3:16">
       <c r="C20" s="1">
         <v>2008</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E20" s="7" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F20" s="7" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="G20" s="1"/>
       <c r="H20" s="1">
@@ -2104,22 +2159,25 @@
       <c r="M20" s="1">
         <v>288</v>
       </c>
-      <c r="O20" s="2" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="21" s="2" customFormat="1" customHeight="1" spans="3:15">
+      <c r="N20" s="1">
+        <v>1</v>
+      </c>
+      <c r="P20" s="2" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="21" s="2" customFormat="1" customHeight="1" spans="3:16">
       <c r="C21" s="1">
         <v>2009</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E21" s="7" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F21" s="7" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="G21" s="1"/>
       <c r="H21" s="1">
@@ -2140,22 +2198,25 @@
       <c r="M21" s="1">
         <v>288</v>
       </c>
-      <c r="O21" s="2" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="22" s="2" customFormat="1" customHeight="1" spans="3:15">
+      <c r="N21" s="1">
+        <v>1</v>
+      </c>
+      <c r="P21" s="2" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="22" s="2" customFormat="1" customHeight="1" spans="3:16">
       <c r="C22" s="1">
         <v>2010</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E22" s="7" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F22" s="7" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G22" s="1"/>
       <c r="H22" s="1">
@@ -2176,22 +2237,25 @@
       <c r="M22" s="1">
         <v>288</v>
       </c>
-      <c r="O22" s="2" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="23" s="2" customFormat="1" customHeight="1" spans="3:15">
+      <c r="N22" s="1">
+        <v>1</v>
+      </c>
+      <c r="P22" s="2" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="23" s="2" customFormat="1" customHeight="1" spans="3:16">
       <c r="C23" s="1">
         <v>2011</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E23" s="7" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="F23" s="7" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G23" s="1"/>
       <c r="H23" s="1">
@@ -2212,22 +2276,25 @@
       <c r="M23" s="1">
         <v>288</v>
       </c>
-      <c r="O23" s="2" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="24" s="2" customFormat="1" customHeight="1" spans="3:15">
+      <c r="N23" s="1">
+        <v>1</v>
+      </c>
+      <c r="P23" s="2" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="24" s="2" customFormat="1" customHeight="1" spans="3:16">
       <c r="C24" s="1">
         <v>2012</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E24" s="7" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="F24" s="7" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G24" s="1"/>
       <c r="H24" s="1">
@@ -2248,11 +2315,14 @@
       <c r="M24" s="1">
         <v>288</v>
       </c>
-      <c r="O24" s="2" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="25" s="2" customFormat="1" customHeight="1" spans="3:15">
+      <c r="N24" s="1">
+        <v>1</v>
+      </c>
+      <c r="P24" s="2" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="25" s="2" customFormat="1" customHeight="1" spans="3:16">
       <c r="C25" s="1"/>
       <c r="E25" s="1"/>
       <c r="F25" s="1"/>
@@ -2261,18 +2331,18 @@
       <c r="I25" s="1"/>
       <c r="J25" s="1"/>
     </row>
-    <row r="26" s="2" customFormat="1" customHeight="1" spans="3:15">
+    <row r="26" s="2" customFormat="1" customHeight="1" spans="3:16">
       <c r="C26" s="1">
         <v>3001</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="E26" s="7" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F26" s="7" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G26" s="1"/>
       <c r="H26" s="1">
@@ -2293,22 +2363,25 @@
       <c r="M26" s="1">
         <v>666</v>
       </c>
-      <c r="O26" s="2" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="27" s="2" customFormat="1" customHeight="1" spans="3:15">
+      <c r="N26" s="1">
+        <v>1</v>
+      </c>
+      <c r="P26" s="2" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="27" s="2" customFormat="1" customHeight="1" spans="3:16">
       <c r="C27" s="1">
         <v>3002</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E27" s="7" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="F27" s="7" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="G27" s="1"/>
       <c r="H27" s="1">
@@ -2329,22 +2402,25 @@
       <c r="M27" s="1">
         <v>666</v>
       </c>
-      <c r="O27" s="2" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="28" s="2" customFormat="1" customHeight="1" spans="3:15">
+      <c r="N27" s="1">
+        <v>1</v>
+      </c>
+      <c r="P27" s="2" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="28" s="2" customFormat="1" customHeight="1" spans="3:16">
       <c r="C28" s="1">
         <v>3003</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="E28" s="7" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="F28" s="7" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G28" s="1"/>
       <c r="H28" s="1">
@@ -2365,22 +2441,25 @@
       <c r="M28" s="1">
         <v>666</v>
       </c>
-      <c r="O28" s="2" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="29" s="2" customFormat="1" customHeight="1" spans="3:15">
+      <c r="N28" s="1">
+        <v>1</v>
+      </c>
+      <c r="P28" s="2" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="29" s="2" customFormat="1" customHeight="1" spans="3:16">
       <c r="C29" s="1">
         <v>3004</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="E29" s="7" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F29" s="7" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="G29" s="1"/>
       <c r="H29" s="1">
@@ -2401,22 +2480,25 @@
       <c r="M29" s="1">
         <v>666</v>
       </c>
-      <c r="O29" s="2" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="30" s="2" customFormat="1" customHeight="1" spans="3:15">
+      <c r="N29" s="1">
+        <v>1</v>
+      </c>
+      <c r="P29" s="2" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="30" s="2" customFormat="1" customHeight="1" spans="3:16">
       <c r="C30" s="1">
         <v>3005</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E30" s="7" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="F30" s="7" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G30" s="1"/>
       <c r="H30" s="1">
@@ -2437,22 +2519,25 @@
       <c r="M30" s="1">
         <v>666</v>
       </c>
-      <c r="O30" s="2" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="31" s="2" customFormat="1" customHeight="1" spans="3:15">
+      <c r="N30" s="1">
+        <v>1</v>
+      </c>
+      <c r="P30" s="2" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="31" s="2" customFormat="1" customHeight="1" spans="3:16">
       <c r="C31" s="1">
         <v>3006</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E31" s="7" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="F31" s="7" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G31" s="1"/>
       <c r="H31" s="1">
@@ -2473,22 +2558,25 @@
       <c r="M31" s="1">
         <v>666</v>
       </c>
-      <c r="O31" s="2" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="32" s="2" customFormat="1" customHeight="1" spans="3:15">
+      <c r="N31" s="1">
+        <v>1</v>
+      </c>
+      <c r="P31" s="2" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="32" s="2" customFormat="1" customHeight="1" spans="3:16">
       <c r="C32" s="1">
         <v>3007</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="E32" s="7" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="F32" s="7" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="G32" s="1"/>
       <c r="H32" s="1">
@@ -2509,22 +2597,25 @@
       <c r="M32" s="1">
         <v>666</v>
       </c>
-      <c r="O32" s="2" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="33" s="2" customFormat="1" customHeight="1" spans="3:16">
+      <c r="N32" s="1">
+        <v>1</v>
+      </c>
+      <c r="P32" s="2" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="33" s="2" customFormat="1" customHeight="1" spans="3:17">
       <c r="C33" s="1">
         <v>3008</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="E33" s="7" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="F33" s="7" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="G33" s="1"/>
       <c r="H33" s="1">
@@ -2545,11 +2636,14 @@
       <c r="M33" s="1">
         <v>666</v>
       </c>
-      <c r="O33" s="2" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="36" s="2" customFormat="1" customHeight="1" spans="3:16">
+      <c r="N33" s="1">
+        <v>1</v>
+      </c>
+      <c r="P33" s="2" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="36" s="2" customFormat="1" customHeight="1" spans="3:17">
       <c r="C36" s="1"/>
       <c r="E36" s="1"/>
       <c r="F36" s="1"/>
@@ -2558,18 +2652,18 @@
       <c r="I36" s="1"/>
       <c r="J36" s="1"/>
     </row>
-    <row r="37" s="2" customFormat="1" customHeight="1" spans="3:16">
+    <row r="37" s="2" customFormat="1" customHeight="1" spans="3:17">
       <c r="C37" s="1">
         <v>4001</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="E37" s="8" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="F37" s="7" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="G37" s="1"/>
       <c r="H37" s="1">
@@ -2590,25 +2684,28 @@
       <c r="M37" s="1">
         <v>2888</v>
       </c>
-      <c r="O37" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="P37" s="1" t="s">
+      <c r="N37" s="1">
+        <v>1</v>
+      </c>
+      <c r="P37" s="2" t="s">
         <v>98</v>
       </c>
-    </row>
-    <row r="38" s="2" customFormat="1" customHeight="1" spans="3:16">
+      <c r="Q37" s="1" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="38" s="2" customFormat="1" customHeight="1" spans="3:17">
       <c r="C38" s="1">
         <v>4002</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E38" s="8" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="F38" s="7" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="G38" s="1"/>
       <c r="H38" s="1">
@@ -2629,25 +2726,28 @@
       <c r="M38" s="1">
         <v>2888</v>
       </c>
-      <c r="O38" s="2" t="s">
-        <v>100</v>
+      <c r="N38" s="1">
+        <v>1</v>
       </c>
       <c r="P38" s="2" t="s">
         <v>101</v>
       </c>
-    </row>
-    <row r="39" s="2" customFormat="1" customHeight="1" spans="3:16">
+      <c r="Q38" s="2" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="39" s="2" customFormat="1" customHeight="1" spans="3:17">
       <c r="C39" s="1">
         <v>4003</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="E39" s="8" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="F39" s="7" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="G39" s="1"/>
       <c r="H39" s="1">
@@ -2668,22 +2768,25 @@
       <c r="M39" s="1">
         <v>2888</v>
       </c>
-      <c r="O39" s="2" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="40" s="2" customFormat="1" customHeight="1" spans="3:16">
+      <c r="N39" s="1">
+        <v>1</v>
+      </c>
+      <c r="P39" s="2" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="40" s="2" customFormat="1" customHeight="1" spans="3:17">
       <c r="C40" s="1">
         <v>4004</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="E40" s="8" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="F40" s="7" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="G40" s="1"/>
       <c r="H40" s="1">
@@ -2704,22 +2807,25 @@
       <c r="M40" s="1">
         <v>2888</v>
       </c>
-      <c r="O40" s="2" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="41" s="2" customFormat="1" customHeight="1" spans="3:16">
+      <c r="N40" s="1">
+        <v>1</v>
+      </c>
+      <c r="P40" s="2" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="41" s="2" customFormat="1" customHeight="1" spans="3:17">
       <c r="C41" s="1">
         <v>4005</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="E41" s="8" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="F41" s="7" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="G41" s="1"/>
       <c r="H41" s="1">
@@ -2740,22 +2846,25 @@
       <c r="M41" s="1">
         <v>2888</v>
       </c>
-      <c r="O41" s="2" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="42" s="2" customFormat="1" customHeight="1" spans="3:16">
+      <c r="N41" s="1">
+        <v>1</v>
+      </c>
+      <c r="P41" s="2" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="42" s="2" customFormat="1" customHeight="1" spans="3:17">
       <c r="C42" s="1">
         <v>4006</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="E42" s="8" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="F42" s="7" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="G42" s="1"/>
       <c r="H42" s="1">
@@ -2776,22 +2885,25 @@
       <c r="M42" s="1">
         <v>2888</v>
       </c>
-      <c r="O42" s="2" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="43" s="2" customFormat="1" customHeight="1" spans="3:16">
+      <c r="N42" s="1">
+        <v>1</v>
+      </c>
+      <c r="P42" s="2" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="43" s="2" customFormat="1" customHeight="1" spans="3:17">
       <c r="C43" s="1">
         <v>4007</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E43" s="8" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="F43" s="7" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="G43" s="1"/>
       <c r="H43" s="1">
@@ -2812,22 +2924,25 @@
       <c r="M43" s="1">
         <v>2888</v>
       </c>
-      <c r="O43" s="2" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="44" s="2" customFormat="1" customHeight="1" spans="3:16">
+      <c r="N43" s="1">
+        <v>1</v>
+      </c>
+      <c r="P43" s="2" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="44" s="2" customFormat="1" customHeight="1" spans="3:17">
       <c r="C44" s="1">
         <v>4008</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="E44" s="8" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="F44" s="7" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="G44" s="1"/>
       <c r="H44" s="1">
@@ -2848,22 +2963,25 @@
       <c r="M44" s="1">
         <v>2888</v>
       </c>
-      <c r="O44" s="2" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="45" s="2" customFormat="1" customHeight="1" spans="3:16">
+      <c r="N44" s="1">
+        <v>1</v>
+      </c>
+      <c r="P44" s="2" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="45" s="2" customFormat="1" customHeight="1" spans="3:17">
       <c r="C45" s="1">
         <v>4009</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="E45" s="8" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="F45" s="7" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="G45" s="1"/>
       <c r="H45" s="1">
@@ -2884,23 +3002,26 @@
       <c r="M45" s="1">
         <v>2888</v>
       </c>
-      <c r="N45" s="1"/>
-      <c r="O45" s="1" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="46" s="2" customFormat="1" customHeight="1" spans="3:16">
+      <c r="N45" s="1">
+        <v>1</v>
+      </c>
+      <c r="O45" s="1"/>
+      <c r="P45" s="1" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="46" s="2" customFormat="1" customHeight="1" spans="3:17">
       <c r="C46" s="1">
         <v>4010</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="E46" s="8" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="F46" s="7" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="G46" s="1"/>
       <c r="H46" s="1">
@@ -2921,23 +3042,26 @@
       <c r="M46" s="1">
         <v>2888</v>
       </c>
-      <c r="N46" s="1"/>
-      <c r="O46" s="1" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="47" s="2" customFormat="1" customHeight="1" spans="3:16">
+      <c r="N46" s="1">
+        <v>1</v>
+      </c>
+      <c r="O46" s="1"/>
+      <c r="P46" s="1" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="47" s="2" customFormat="1" customHeight="1" spans="3:17">
       <c r="C47" s="1">
         <v>4011</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="E47" s="8" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="F47" s="7" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="G47" s="1"/>
       <c r="H47" s="1">
@@ -2958,23 +3082,26 @@
       <c r="M47" s="1">
         <v>2888</v>
       </c>
-      <c r="N47" s="1"/>
-      <c r="O47" s="1" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="48" s="2" customFormat="1" customHeight="1" spans="3:16">
+      <c r="N47" s="1">
+        <v>1</v>
+      </c>
+      <c r="O47" s="1"/>
+      <c r="P47" s="1" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="48" s="2" customFormat="1" customHeight="1" spans="3:17">
       <c r="C48" s="1">
         <v>4012</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="E48" s="8" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="F48" s="7" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="G48" s="1"/>
       <c r="H48" s="1">
@@ -2995,23 +3122,26 @@
       <c r="M48" s="1">
         <v>2888</v>
       </c>
-      <c r="N48" s="1"/>
-      <c r="O48" s="1" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="49" s="2" customFormat="1" customHeight="1" spans="3:15">
+      <c r="N48" s="1">
+        <v>1</v>
+      </c>
+      <c r="O48" s="1"/>
+      <c r="P48" s="1" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="49" s="2" customFormat="1" customHeight="1" spans="3:16">
       <c r="C49" s="1">
         <v>4013</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="E49" s="8" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="F49" s="7" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="G49" s="1">
         <v>40001</v>
@@ -3030,22 +3160,25 @@
       <c r="M49" s="1">
         <v>2888</v>
       </c>
-      <c r="N49" s="2" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="50" s="2" customFormat="1" customHeight="1" spans="3:15">
+      <c r="N49" s="1">
+        <v>1</v>
+      </c>
+      <c r="O49" s="2" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="50" s="2" customFormat="1" customHeight="1" spans="3:16">
       <c r="C50" s="1">
         <v>4014</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="E50" s="8" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="F50" s="7" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="G50" s="1">
         <v>40002</v>
@@ -3064,22 +3197,25 @@
       <c r="M50" s="1">
         <v>2888</v>
       </c>
-      <c r="N50" s="2" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="51" s="2" customFormat="1" customHeight="1" spans="3:15">
+      <c r="N50" s="1">
+        <v>1</v>
+      </c>
+      <c r="O50" s="2" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="51" s="2" customFormat="1" customHeight="1" spans="3:16">
       <c r="C51" s="1">
         <v>4015</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="E51" s="8" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="F51" s="7" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="G51" s="1">
         <v>40003</v>
@@ -3098,11 +3234,14 @@
       <c r="M51" s="1">
         <v>2888</v>
       </c>
-      <c r="N51" s="2" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="52" s="2" customFormat="1" customHeight="1" spans="3:15">
+      <c r="N51" s="1">
+        <v>1</v>
+      </c>
+      <c r="O51" s="2" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="52" s="2" customFormat="1" customHeight="1" spans="3:16">
       <c r="C52" s="1"/>
       <c r="E52" s="4"/>
       <c r="F52" s="1"/>
@@ -3111,7 +3250,7 @@
       <c r="I52" s="1"/>
       <c r="J52" s="1"/>
     </row>
-    <row r="53" s="2" customFormat="1" customHeight="1" spans="3:15">
+    <row r="53" s="2" customFormat="1" customHeight="1" spans="3:16">
       <c r="C53" s="1"/>
       <c r="E53" s="4"/>
       <c r="F53" s="1"/>
@@ -3120,7 +3259,7 @@
       <c r="I53" s="1"/>
       <c r="J53" s="1"/>
     </row>
-    <row r="54" s="2" customFormat="1" customHeight="1" spans="3:15">
+    <row r="54" s="2" customFormat="1" customHeight="1" spans="3:16">
       <c r="C54" s="1"/>
       <c r="E54" s="4"/>
       <c r="F54" s="1"/>
@@ -3129,18 +3268,18 @@
       <c r="I54" s="1"/>
       <c r="J54" s="1"/>
     </row>
-    <row r="55" s="2" customFormat="1" customHeight="1" spans="3:15">
+    <row r="55" s="2" customFormat="1" customHeight="1" spans="3:16">
       <c r="C55" s="1">
         <v>5001</v>
       </c>
       <c r="D55" s="5" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="E55" s="7" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="F55" s="7" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="G55" s="1"/>
       <c r="H55" s="1">
@@ -3161,22 +3300,25 @@
       <c r="M55" s="1">
         <v>8888</v>
       </c>
-      <c r="O55" s="2" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="56" s="2" customFormat="1" customHeight="1" spans="3:15">
+      <c r="N55" s="1">
+        <v>1</v>
+      </c>
+      <c r="P55" s="2" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="56" s="2" customFormat="1" customHeight="1" spans="3:16">
       <c r="C56" s="1">
         <v>5002</v>
       </c>
       <c r="D56" s="6" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="E56" s="7" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="F56" s="7" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="G56" s="1"/>
       <c r="H56" s="1">
@@ -3197,22 +3339,25 @@
       <c r="M56" s="1">
         <v>8888</v>
       </c>
-      <c r="N56" s="2" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="57" s="2" customFormat="1" customHeight="1" spans="3:15">
+      <c r="N56" s="1">
+        <v>1</v>
+      </c>
+      <c r="O56" s="2" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="57" s="2" customFormat="1" customHeight="1" spans="3:16">
       <c r="C57" s="1">
         <v>5003</v>
       </c>
       <c r="D57" s="6" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="E57" s="7" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="F57" s="7" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="G57" s="1"/>
       <c r="H57" s="1">
@@ -3233,22 +3378,25 @@
       <c r="M57" s="1">
         <v>8888</v>
       </c>
-      <c r="O57" s="2" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="58" s="2" customFormat="1" customHeight="1" spans="3:15">
+      <c r="N57" s="1">
+        <v>1</v>
+      </c>
+      <c r="P57" s="2" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="58" s="2" customFormat="1" customHeight="1" spans="3:16">
       <c r="C58" s="1">
         <v>5004</v>
       </c>
       <c r="D58" s="6" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="E58" s="7" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="F58" s="7" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="H58" s="2">
         <v>0</v>
@@ -3268,22 +3416,25 @@
       <c r="M58" s="1">
         <v>8888</v>
       </c>
-      <c r="N58" s="2" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="59" s="2" customFormat="1" customHeight="1" spans="3:15">
+      <c r="N58" s="1">
+        <v>1</v>
+      </c>
+      <c r="O58" s="2" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="59" s="2" customFormat="1" customHeight="1" spans="3:16">
       <c r="C59" s="1">
         <v>5005</v>
       </c>
       <c r="D59" s="6" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="E59" s="7" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="F59" s="7" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="G59" s="1"/>
       <c r="H59" s="1">
@@ -3304,22 +3455,25 @@
       <c r="M59" s="1">
         <v>8888</v>
       </c>
-      <c r="O59" s="2" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="60" customHeight="1" spans="3:15">
+      <c r="N59" s="1">
+        <v>1</v>
+      </c>
+      <c r="P59" s="2" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="60" customHeight="1" spans="3:16">
       <c r="C60" s="1">
         <v>5006</v>
       </c>
       <c r="D60" s="5" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="E60" s="7" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="F60" s="7" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="H60" s="1">
         <v>7</v>
@@ -3339,22 +3493,25 @@
       <c r="M60" s="1">
         <v>8888</v>
       </c>
-      <c r="O60" s="1" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="61" customHeight="1" spans="3:15">
+      <c r="N60" s="1">
+        <v>1</v>
+      </c>
+      <c r="P60" s="1" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="61" customHeight="1" spans="3:16">
       <c r="C61" s="1">
         <v>5007</v>
       </c>
       <c r="D61" s="1" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="E61" s="7" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="F61" s="7" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="H61" s="1">
         <v>8</v>
@@ -3374,22 +3531,25 @@
       <c r="M61" s="1">
         <v>8888</v>
       </c>
-      <c r="O61" s="1" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="62" customHeight="1" spans="3:15">
+      <c r="N61" s="1">
+        <v>1</v>
+      </c>
+      <c r="P61" s="1" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="62" customHeight="1" spans="3:16">
       <c r="C62" s="1">
         <v>5008</v>
       </c>
       <c r="D62" s="1" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="E62" s="7" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="F62" s="7" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="H62" s="1">
         <v>21000</v>
@@ -3409,22 +3569,25 @@
       <c r="M62" s="1">
         <v>8888</v>
       </c>
-      <c r="O62" s="1" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="63" customHeight="1" spans="3:15">
+      <c r="N62" s="1">
+        <v>1</v>
+      </c>
+      <c r="P62" s="1" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="63" customHeight="1" spans="3:16">
       <c r="C63" s="1">
         <v>5009</v>
       </c>
       <c r="D63" s="6" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="E63" s="7" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="F63" s="7" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="H63" s="1">
         <v>81</v>
@@ -3444,22 +3607,25 @@
       <c r="M63" s="1">
         <v>8888</v>
       </c>
-      <c r="O63" s="1" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="64" customHeight="1" spans="3:15">
+      <c r="N63" s="1">
+        <v>1</v>
+      </c>
+      <c r="P63" s="1" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="64" customHeight="1" spans="3:16">
       <c r="C64" s="1">
         <v>5010</v>
       </c>
       <c r="D64" s="6" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="E64" s="7" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="F64" s="7" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="H64" s="1">
         <v>82</v>
@@ -3479,22 +3645,25 @@
       <c r="M64" s="1">
         <v>8888</v>
       </c>
-      <c r="O64" s="1" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="65" customHeight="1" spans="3:15">
+      <c r="N64" s="1">
+        <v>1</v>
+      </c>
+      <c r="P64" s="1" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="65" customHeight="1" spans="3:16">
       <c r="C65" s="1">
         <v>5011</v>
       </c>
       <c r="D65" s="6" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E65" s="7" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="F65" s="7" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="H65" s="1">
         <v>83</v>
@@ -3514,22 +3683,25 @@
       <c r="M65" s="1">
         <v>8888</v>
       </c>
-      <c r="O65" s="1" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="66" customHeight="1" spans="3:15">
+      <c r="N65" s="1">
+        <v>1</v>
+      </c>
+      <c r="P65" s="1" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="66" customHeight="1" spans="3:16">
       <c r="C66" s="1">
         <v>5012</v>
       </c>
       <c r="D66" s="6" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="E66" s="7" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="F66" s="7" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="H66" s="1">
         <v>84</v>
@@ -3549,8 +3721,54 @@
       <c r="M66" s="1">
         <v>8888</v>
       </c>
-      <c r="O66" s="1" t="s">
-        <v>148</v>
+      <c r="N66" s="1">
+        <v>1</v>
+      </c>
+      <c r="P66" s="1" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="67" customHeight="1" spans="3:16">
+      <c r="D67" s="6"/>
+      <c r="K67" s="2"/>
+    </row>
+    <row r="68" customHeight="1" spans="3:16">
+      <c r="C68" s="1">
+        <v>6001</v>
+      </c>
+      <c r="D68" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="E68" s="7" t="s">
+        <v>126</v>
+      </c>
+      <c r="F68" s="7" t="s">
+        <v>97</v>
+      </c>
+      <c r="H68" s="1">
+        <v>111</v>
+      </c>
+      <c r="I68" s="1">
+        <v>1</v>
+      </c>
+      <c r="J68" s="1">
+        <v>1</v>
+      </c>
+      <c r="K68" s="2">
+        <v>7</v>
+      </c>
+      <c r="L68" s="1">
+        <v>1</v>
+      </c>
+      <c r="M68" s="1">
+        <v>8888</v>
+      </c>
+      <c r="N68" s="1">
+        <v>0</v>
+      </c>
+      <c r="O68" s="2"/>
+      <c r="P68" s="2" t="s">
+        <v>131</v>
       </c>
     </row>
   </sheetData>
